--- a/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197570EE-92F4-4A41-BB83-57FB058B4FA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E880765B-5B97-4B14-B9CB-7B468BF8E643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="870" windowWidth="14580" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -273,9 +273,6 @@
     <t>unavailable</t>
   </si>
   <si>
-    <t>DEGS1_P2</t>
-  </si>
-  <si>
     <t>direct_mapping</t>
   </si>
   <si>
@@ -364,13 +361,16 @@
   </si>
   <si>
     <t>This comes from DEGS1</t>
+  </si>
+  <si>
+    <t>BGS98_P2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,6 +399,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -421,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -440,9 +454,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -459,9 +477,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -499,9 +517,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -534,26 +552,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -586,26 +587,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -780,7 +764,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="47.85546875" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
@@ -838,7 +822,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>80</v>
@@ -863,23 +847,23 @@
       <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>82</v>
+      <c r="E3" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="J3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -892,23 +876,23 @@
       <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="H4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
         <v>84</v>
-      </c>
-      <c r="J4" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -921,23 +905,23 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="H5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" t="s">
         <v>84</v>
-      </c>
-      <c r="J5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -951,22 +935,22 @@
         <v>13</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -979,26 +963,26 @@
       <c r="D7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" t="s">
         <v>82</v>
       </c>
-      <c r="F7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="H7" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" t="s">
         <v>84</v>
-      </c>
-      <c r="I7" t="s">
-        <v>112</v>
-      </c>
-      <c r="J7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1011,8 +995,8 @@
       <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
-        <v>82</v>
+      <c r="E8" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G8" t="s">
         <v>80</v>
@@ -1021,7 +1005,7 @@
         <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s">
         <v>80</v>
@@ -1040,8 +1024,8 @@
       <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" t="s">
-        <v>82</v>
+      <c r="E9" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
@@ -1050,7 +1034,7 @@
         <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J9" t="s">
         <v>80</v>
@@ -1069,26 +1053,26 @@
       <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" t="s">
         <v>82</v>
       </c>
-      <c r="F10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="H10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" t="s">
         <v>84</v>
-      </c>
-      <c r="I10" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" t="s">
-        <v>84</v>
-      </c>
-      <c r="K10" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1102,22 +1086,22 @@
         <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1131,22 +1115,22 @@
         <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1159,26 +1143,26 @@
       <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" t="s">
         <v>82</v>
       </c>
-      <c r="F13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="H13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" t="s">
         <v>84</v>
-      </c>
-      <c r="I13" t="s">
-        <v>112</v>
-      </c>
-      <c r="J13" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1191,8 +1175,8 @@
       <c r="D14" t="s">
         <v>13</v>
       </c>
-      <c r="E14" t="s">
-        <v>82</v>
+      <c r="E14" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G14" t="s">
         <v>80</v>
@@ -1217,8 +1201,8 @@
       <c r="D15" t="s">
         <v>13</v>
       </c>
-      <c r="E15" t="s">
-        <v>82</v>
+      <c r="E15" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G15" t="s">
         <v>80</v>
@@ -1243,8 +1227,8 @@
       <c r="D16" t="s">
         <v>13</v>
       </c>
-      <c r="E16" t="s">
-        <v>82</v>
+      <c r="E16" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G16" t="s">
         <v>80</v>
@@ -1269,8 +1253,8 @@
       <c r="D17" t="s">
         <v>13</v>
       </c>
-      <c r="E17" t="s">
-        <v>82</v>
+      <c r="E17" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G17" t="s">
         <v>80</v>
@@ -1295,8 +1279,8 @@
       <c r="D18" t="s">
         <v>13</v>
       </c>
-      <c r="E18" t="s">
-        <v>82</v>
+      <c r="E18" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="G18" t="s">
         <v>80</v>
@@ -1322,23 +1306,23 @@
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>84</v>
+      <c r="H19" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -1352,23 +1336,23 @@
         <v>13</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>84</v>
+      <c r="H20" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -1382,23 +1366,23 @@
         <v>13</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>84</v>
+      <c r="H21" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
@@ -1412,23 +1396,23 @@
         <v>13</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>84</v>
+      <c r="H22" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
@@ -1442,23 +1426,23 @@
         <v>13</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>84</v>
+      <c r="H23" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
@@ -1472,23 +1456,23 @@
         <v>13</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>84</v>
+      <c r="H24" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1502,7 +1486,7 @@
         <v>13</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
@@ -1523,30 +1507,30 @@
       <c r="B26" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>84</v>
+      <c r="H26" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1560,23 +1544,23 @@
         <v>13</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>84</v>
+      <c r="H27" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -1590,7 +1574,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
@@ -1618,7 +1602,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
@@ -1646,7 +1630,7 @@
         <v>13</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
@@ -1674,7 +1658,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
@@ -1702,7 +1686,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
@@ -1730,7 +1714,7 @@
         <v>13</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
@@ -1758,7 +1742,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
@@ -1780,29 +1764,29 @@
         <v>78</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>84</v>
+      <c r="H35" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
@@ -1810,32 +1794,33 @@
         <v>79</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E880765B-5B97-4B14-B9CB-7B468BF8E643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5467EB-4804-43E9-85EA-BDC86F1FFC3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="113">
   <si>
     <t>index</t>
   </si>
@@ -285,9 +285,6 @@
     <t>N/A adult participants</t>
   </si>
   <si>
-    <t>Ushuef</t>
-  </si>
-  <si>
     <t>LBhdl</t>
   </si>
   <si>
@@ -315,27 +312,12 @@
     <t>USbmi</t>
   </si>
   <si>
-    <t>Usbmi_FUP</t>
-  </si>
-  <si>
-    <t>Ustail_FUP</t>
-  </si>
-  <si>
-    <t>Ustail</t>
-  </si>
-  <si>
-    <t>Ushuef_FUP</t>
-  </si>
-  <si>
     <t>Gcal</t>
   </si>
   <si>
     <t>GFP</t>
   </si>
   <si>
-    <t>GKM</t>
-  </si>
-  <si>
     <t>GZE</t>
   </si>
   <si>
@@ -357,13 +339,31 @@
     <t>GZB</t>
   </si>
   <si>
-    <t>Fett</t>
-  </si>
-  <si>
     <t>This comes from DEGS1</t>
   </si>
   <si>
     <t>BGS98_P2</t>
+  </si>
+  <si>
+    <t>GZA</t>
+  </si>
+  <si>
+    <t>GMNa * 1000</t>
+  </si>
+  <si>
+    <t>UStail_FUP</t>
+  </si>
+  <si>
+    <t>UStail</t>
+  </si>
+  <si>
+    <t>USbmi_FUP</t>
+  </si>
+  <si>
+    <t>UShuef</t>
+  </si>
+  <si>
+    <t>UShuef_FUP</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -455,12 +455,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -477,9 +474,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -517,9 +514,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -552,9 +549,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -587,9 +601,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -764,7 +795,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="47.85546875" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
@@ -822,7 +853,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>80</v>
@@ -848,22 +879,22 @@
         <v>13</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="G3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -877,16 +908,16 @@
         <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
         <v>82</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>83</v>
+      <c r="H4" t="s">
+        <v>82</v>
       </c>
       <c r="J4" t="s">
         <v>83</v>
@@ -906,16 +937,16 @@
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G5" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>83</v>
+      <c r="H5" t="s">
+        <v>82</v>
       </c>
       <c r="J5" t="s">
         <v>83</v>
@@ -935,16 +966,16 @@
         <v>13</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>83</v>
+      <c r="H6" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>83</v>
@@ -964,19 +995,19 @@
         <v>13</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G7" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>83</v>
+      <c r="H7" t="s">
+        <v>82</v>
       </c>
       <c r="I7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J7" t="s">
         <v>83</v>
@@ -996,7 +1027,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G8" t="s">
         <v>80</v>
@@ -1025,7 +1056,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
@@ -1054,19 +1085,19 @@
         <v>13</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G10" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>83</v>
+      <c r="H10" t="s">
+        <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
         <v>83</v>
@@ -1086,16 +1117,16 @@
         <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>83</v>
+      <c r="H11" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>83</v>
@@ -1115,16 +1146,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>83</v>
+      <c r="H12" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>83</v>
@@ -1144,19 +1175,19 @@
         <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" t="s">
         <v>112</v>
       </c>
-      <c r="F13" t="s">
-        <v>99</v>
-      </c>
       <c r="G13" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>83</v>
+      <c r="H13" t="s">
+        <v>82</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J13" t="s">
         <v>83</v>
@@ -1176,7 +1207,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s">
         <v>80</v>
@@ -1202,7 +1233,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s">
         <v>80</v>
@@ -1228,7 +1259,7 @@
         <v>13</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G16" t="s">
         <v>80</v>
@@ -1254,7 +1285,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G17" t="s">
         <v>80</v>
@@ -1280,7 +1311,7 @@
         <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G18" t="s">
         <v>80</v>
@@ -1306,16 +1337,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>83</v>
+      <c r="H19" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
@@ -1336,16 +1367,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>83</v>
+      <c r="H20" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
@@ -1366,16 +1397,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="8" t="s">
-        <v>83</v>
+      <c r="H21" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
@@ -1396,16 +1427,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>83</v>
+      <c r="H22" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
@@ -1426,16 +1457,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>83</v>
+      <c r="H23" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
@@ -1456,16 +1487,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="8" t="s">
-        <v>83</v>
+      <c r="H24" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
@@ -1486,7 +1517,7 @@
         <v>13</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
@@ -1507,30 +1538,28 @@
       <c r="B26" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>102</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F26" s="8"/>
       <c r="G26" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1544,16 +1573,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>83</v>
+      <c r="H27" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
@@ -1574,7 +1603,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
@@ -1602,7 +1631,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
@@ -1630,7 +1659,7 @@
         <v>13</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
@@ -1658,7 +1687,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
@@ -1686,7 +1715,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
@@ -1714,7 +1743,7 @@
         <v>13</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
@@ -1742,7 +1771,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
@@ -1764,29 +1793,29 @@
         <v>78</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>83</v>
+        <v>100</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
@@ -1794,29 +1823,29 @@
         <v>79</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5467EB-4804-43E9-85EA-BDC86F1FFC3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8648B0C2-71B5-44F7-9D79-F6D008698049}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="118">
   <si>
     <t>index</t>
   </si>
@@ -364,13 +364,28 @@
   </si>
   <si>
     <t>UShuef_FUP</t>
+  </si>
+  <si>
+    <t>GFS</t>
+  </si>
+  <si>
+    <t>GFU</t>
+  </si>
+  <si>
+    <t>GKD;GKM</t>
+  </si>
+  <si>
+    <t>GKD+GKM</t>
+  </si>
+  <si>
+    <t>Total sugars (monosaccharides + disaccharides)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,14 +420,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -435,7 +442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -454,7 +461,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,7 +808,7 @@
     <col min="6" max="6" width="13.140625" customWidth="1"/>
     <col min="7" max="7" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.85546875" customWidth="1"/>
   </cols>
@@ -1313,17 +1319,20 @@
       <c r="E18" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" t="s">
-        <v>80</v>
-      </c>
-      <c r="K18" t="s">
-        <v>81</v>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -1519,19 +1528,21 @@
       <c r="E25" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="G25" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -1547,19 +1558,21 @@
       <c r="E26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="8"/>
+      <c r="F26" s="5" t="s">
+        <v>114</v>
+      </c>
       <c r="G26" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1605,19 +1618,23 @@
       <c r="E28" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>115</v>
+      </c>
       <c r="G28" s="5" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I28" s="5"/>
+        <v>116</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="J28" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">

--- a/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
+++ b/analyst/Ines/rmonize/data_proc_elem/DPE_BGS98_INES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Ines\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8648B0C2-71B5-44F7-9D79-F6D008698049}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD034704-9B26-46FC-A445-9084B3C8A7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="120">
   <si>
     <t>index</t>
   </si>
@@ -369,9 +369,6 @@
     <t>GFS</t>
   </si>
   <si>
-    <t>GFU</t>
-  </si>
-  <si>
     <t>GKD;GKM</t>
   </si>
   <si>
@@ -379,6 +376,15 @@
   </si>
   <si>
     <t>Total sugars (monosaccharides + disaccharides)</t>
+  </si>
+  <si>
+    <t>GFU;GFP</t>
+  </si>
+  <si>
+    <t>GFU-GFP</t>
+  </si>
+  <si>
+    <t>Total unsaturated fatty acids - polyunsaturated fatty acids</t>
   </si>
 </sst>
 </file>
@@ -463,7 +469,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -480,9 +486,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -520,9 +526,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -555,26 +561,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -607,26 +596,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -801,7 +773,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="47.85546875" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
@@ -1559,20 +1531,22 @@
         <v>105</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I26" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="J26" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1619,16 +1593,16 @@
         <v>105</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H28" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>83</v>
